--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,893 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127614646</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>438702</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6758712</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127616236</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>439160</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6758708</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127614638</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>438701</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6758712</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127616705</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>438961</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6758546</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127627847</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åsmyrheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>439026</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6758630</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127614683</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>438626</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6758697</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127616623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438985</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6758596</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127616830</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438858</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6758450</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R3" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R4" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127614638</v>
+        <v>127616705</v>
       </c>
       <c r="B5" t="n">
         <v>91350</v>
@@ -1048,17 +1048,26 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438701</v>
+        <v>438961</v>
       </c>
       <c r="R5" t="n">
-        <v>6758712</v>
+        <v>6758546</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127616705</v>
+        <v>127627847</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,46 +1147,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438961</v>
+        <v>439026</v>
       </c>
       <c r="R6" t="n">
-        <v>6758546</v>
+        <v>6758630</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,49 +1207,40 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127627847</v>
+        <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,40 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439026</v>
+        <v>438701</v>
       </c>
       <c r="R7" t="n">
-        <v>6758630</v>
+        <v>6758712</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,30 +1305,39 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,43 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R3" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +915,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R4" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
         <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127627847</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>127614683</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127616623</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R3" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R4" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127616705</v>
+        <v>127627847</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,46 +1031,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438961</v>
+        <v>439026</v>
       </c>
       <c r="R5" t="n">
-        <v>6758546</v>
+        <v>6758630</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,49 +1091,40 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127627847</v>
+        <v>127616705</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,40 +1132,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439026</v>
+        <v>438961</v>
       </c>
       <c r="R6" t="n">
-        <v>6758630</v>
+        <v>6758546</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,30 +1198,39 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127616236</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127627847</v>
+        <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>91358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,40 +1031,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439026</v>
+        <v>438961</v>
       </c>
       <c r="R5" t="n">
-        <v>6758630</v>
+        <v>6758546</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,40 +1097,49 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127616705</v>
+        <v>127614638</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,26 +1164,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438961</v>
+        <v>438701</v>
       </c>
       <c r="R6" t="n">
-        <v>6758546</v>
+        <v>6758712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127614638</v>
+        <v>127627847</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1254,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438701</v>
+        <v>439026</v>
       </c>
       <c r="R7" t="n">
-        <v>6758712</v>
+        <v>6758630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,39 +1314,30 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B3" t="n">
-        <v>91358</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,43 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R3" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +915,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R4" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127616705</v>
+        <v>127627847</v>
       </c>
       <c r="B5" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,46 +1031,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438961</v>
+        <v>439026</v>
       </c>
       <c r="R5" t="n">
-        <v>6758546</v>
+        <v>6758630</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,49 +1091,40 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127614638</v>
+        <v>127616705</v>
       </c>
       <c r="B6" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,17 +1149,26 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438701</v>
+        <v>438961</v>
       </c>
       <c r="R6" t="n">
-        <v>6758712</v>
+        <v>6758546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127627847</v>
+        <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,40 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439026</v>
+        <v>438701</v>
       </c>
       <c r="R7" t="n">
-        <v>6758630</v>
+        <v>6758712</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,30 +1305,39 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
         <v>127614683</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127616623</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R3" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R4" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127627847</v>
+        <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,40 +1031,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439026</v>
+        <v>438961</v>
       </c>
       <c r="R5" t="n">
-        <v>6758630</v>
+        <v>6758546</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,40 +1097,49 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127616705</v>
+        <v>127627847</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,46 +1147,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438961</v>
+        <v>439026</v>
       </c>
       <c r="R6" t="n">
-        <v>6758546</v>
+        <v>6758630</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,39 +1207,30 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>127614683</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127616623</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,43 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R3" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +915,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R4" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
         <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>127616236</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127627847</v>
+        <v>127614638</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,40 +1147,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439026</v>
+        <v>438701</v>
       </c>
       <c r="R6" t="n">
-        <v>6758630</v>
+        <v>6758712</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,40 +1204,49 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127614638</v>
+        <v>127627847</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1254,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438701</v>
+        <v>439026</v>
       </c>
       <c r="R7" t="n">
-        <v>6758712</v>
+        <v>6758630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,39 +1314,30 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R3" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127616236</v>
+        <v>127614646</v>
       </c>
       <c r="B4" t="n">
-        <v>91371</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439160</v>
+        <v>438702</v>
       </c>
       <c r="R4" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
         <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127614638</v>
       </c>
       <c r="B6" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127616830</v>
       </c>
       <c r="B10" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127616705</v>
+        <v>127627847</v>
       </c>
       <c r="B5" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,46 +1031,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438961</v>
+        <v>439026</v>
       </c>
       <c r="R5" t="n">
-        <v>6758546</v>
+        <v>6758630</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,46 +1091,37 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127614638</v>
+        <v>127616705</v>
       </c>
       <c r="B6" t="n">
         <v>91372</v>
@@ -1164,17 +1149,26 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438701</v>
+        <v>438961</v>
       </c>
       <c r="R6" t="n">
-        <v>6758712</v>
+        <v>6758546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127627847</v>
+        <v>127614638</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,40 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439026</v>
+        <v>438701</v>
       </c>
       <c r="R7" t="n">
-        <v>6758630</v>
+        <v>6758712</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,30 +1305,39 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121475752</v>
+        <v>121475671</v>
       </c>
       <c r="B2" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438996</v>
+        <v>438820</v>
       </c>
       <c r="R2" t="n">
-        <v>6758577</v>
+        <v>6758412</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127616236</v>
+        <v>127614638</v>
       </c>
       <c r="B3" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,26 +810,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439160</v>
+        <v>438701</v>
       </c>
       <c r="R3" t="n">
-        <v>6758708</v>
+        <v>6758712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127614646</v>
+        <v>127616236</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +900,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438702</v>
+        <v>439160</v>
       </c>
       <c r="R4" t="n">
-        <v>6758712</v>
+        <v>6758708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127627847</v>
+        <v>127616705</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,40 +1016,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439026</v>
+        <v>438961</v>
       </c>
       <c r="R5" t="n">
-        <v>6758630</v>
+        <v>6758546</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,40 +1082,49 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127616705</v>
+        <v>127616830</v>
       </c>
       <c r="B6" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,14 +1161,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438961</v>
+        <v>438858</v>
       </c>
       <c r="R6" t="n">
-        <v>6758546</v>
+        <v>6758450</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,32 +1237,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127614638</v>
+        <v>127614683</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438701</v>
+        <v>438626</v>
       </c>
       <c r="R7" t="n">
-        <v>6758712</v>
+        <v>6758697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,14 +1344,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127614683</v>
+        <v>127616623</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1375,14 +1375,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsmyrheden, Åsmyrheden, Dlr</t>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438626</v>
+        <v>438985</v>
       </c>
       <c r="R8" t="n">
-        <v>6758697</v>
+        <v>6758596</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,14 +1451,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127616623</v>
+        <v>127627847</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1480,19 +1480,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flytjärnen, Flytjärnen, Dlr</t>
+          <t>Åsmyrheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438985</v>
+        <v>439026</v>
       </c>
       <c r="R9" t="n">
-        <v>6758596</v>
+        <v>6758630</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,49 +1522,40 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127616830</v>
+        <v>127614646</v>
       </c>
       <c r="B10" t="n">
-        <v>91372</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,31 +1563,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438858</v>
+        <v>438702</v>
       </c>
       <c r="R10" t="n">
-        <v>6758450</v>
+        <v>6758712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1637,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,6 +1666,113 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121475752</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flytjärnen, Flytjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>438996</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6758577</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32222-2025 artfynd.xlsx
+++ b/artfynd/A 32222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121475671</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127614638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127616236</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127616705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127616830</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127614683</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127616623</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627847</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127614646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,8 +1823,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121475752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>